--- a/output/yearly_benthic_cover_iteration_55_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_55_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.09520037525531</v>
+        <v>45.42922771489483</v>
       </c>
       <c r="M2" t="n">
-        <v>100.7237047546608</v>
+        <v>99.84962337665087</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.9676329656405</v>
+        <v>88.0459273450542</v>
       </c>
       <c r="C3" t="n">
-        <v>45.86821505062952</v>
+        <v>45.93012358362086</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228623326805683</v>
+        <v>2.228777275087503</v>
       </c>
       <c r="E3" t="n">
-        <v>5.668675398317897</v>
+        <v>5.708212956870103</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742874442268561</v>
+        <v>0.742925758362501</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95273267459639</v>
+        <v>33.97342387848605</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1722243443538</v>
+        <v>34.17458488467504</v>
       </c>
       <c r="I3" t="n">
-        <v>6.559537515119665</v>
+        <v>6.574716601807366</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642965264178506</v>
+        <v>4.643285989765631</v>
       </c>
       <c r="K3" t="n">
-        <v>12.0323670343595</v>
+        <v>11.95407265494581</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86395282097836</v>
+        <v>48.87981009170966</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7645349059674</v>
+        <v>106.7640063302763</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.03869686305566</v>
+        <v>87.08963295243207</v>
       </c>
       <c r="C4" t="n">
-        <v>42.57501661650365</v>
+        <v>42.6102005597684</v>
       </c>
       <c r="D4" t="n">
-        <v>2.183726533998504</v>
+        <v>2.182498764056086</v>
       </c>
       <c r="E4" t="n">
-        <v>6.467435031951595</v>
+        <v>6.504761199279031</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444328599763977</v>
+        <v>0.7444869822405867</v>
       </c>
       <c r="G4" t="n">
-        <v>33.26873696038398</v>
+        <v>33.26799696602177</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24391155891428</v>
+        <v>34.24640118306699</v>
       </c>
       <c r="I4" t="n">
-        <v>5.477748542978404</v>
+        <v>5.49044421876394</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652705374852485</v>
+        <v>4.653043639003667</v>
       </c>
       <c r="K4" t="n">
-        <v>12.96130313694434</v>
+        <v>12.91036704756793</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28147087113203</v>
+        <v>44.29680137594681</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81779062458001</v>
+        <v>99.81736898328315</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.94139900608124</v>
+        <v>85.8938595389632</v>
       </c>
       <c r="C5" t="n">
-        <v>42.32783193808307</v>
+        <v>42.26653219517915</v>
       </c>
       <c r="D5" t="n">
-        <v>2.130336945500227</v>
+        <v>2.124066494337297</v>
       </c>
       <c r="E5" t="n">
-        <v>7.071461519626767</v>
+        <v>7.094526644214809</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745753219825138</v>
+        <v>0.7458112377489312</v>
       </c>
       <c r="G5" t="n">
-        <v>32.45535481361856</v>
+        <v>32.37730937263697</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30464811195633</v>
+        <v>34.30731693645083</v>
       </c>
       <c r="I5" t="n">
-        <v>4.572886771647121</v>
+        <v>4.583508617643543</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660957623907112</v>
+        <v>4.661320235930821</v>
       </c>
       <c r="K5" t="n">
-        <v>14.05860099391875</v>
+        <v>14.1061404610368</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46140738624877</v>
+        <v>43.47481500437394</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84784031825059</v>
+        <v>99.84748766058989</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.65521144764426</v>
+        <v>84.54315263032525</v>
       </c>
       <c r="C6" t="n">
-        <v>41.75184210286245</v>
+        <v>41.62760525941723</v>
       </c>
       <c r="D6" t="n">
-        <v>2.067664136126715</v>
+        <v>2.058193146737294</v>
       </c>
       <c r="E6" t="n">
-        <v>7.499502369852311</v>
+        <v>7.512063745167559</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468738995922944</v>
+        <v>0.7469361031641943</v>
       </c>
       <c r="G6" t="n">
-        <v>31.50054422852307</v>
+        <v>31.37319685528285</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35619938124553</v>
+        <v>34.35906074555294</v>
       </c>
       <c r="I6" t="n">
-        <v>3.816465559852504</v>
+        <v>3.82535138964421</v>
       </c>
       <c r="J6" t="n">
-        <v>4.66796187245184</v>
+        <v>4.668350644776215</v>
       </c>
       <c r="K6" t="n">
-        <v>15.34478855235574</v>
+        <v>15.45684736967473</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77634471223604</v>
+        <v>42.78822768708461</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87297536745425</v>
+        <v>99.87268031617657</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.09461087208</v>
+        <v>82.80729214808186</v>
       </c>
       <c r="C7" t="n">
-        <v>40.78404871962073</v>
+        <v>40.48582817222574</v>
       </c>
       <c r="D7" t="n">
-        <v>1.991632455510883</v>
+        <v>1.973465278404667</v>
       </c>
       <c r="E7" t="n">
-        <v>7.754474142022842</v>
+        <v>7.734802525294923</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478279859855885</v>
+        <v>0.7478958161131329</v>
       </c>
       <c r="G7" t="n">
-        <v>30.34221330032187</v>
+        <v>30.08168342441664</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40008735533706</v>
+        <v>34.40320754120411</v>
       </c>
       <c r="I7" t="n">
-        <v>3.184450720491819</v>
+        <v>3.191888711941308</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673924912409928</v>
+        <v>4.674348850707081</v>
       </c>
       <c r="K7" t="n">
-        <v>16.90538912792002</v>
+        <v>17.19270785191814</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20454922024113</v>
+        <v>42.21520421503266</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89398706778186</v>
+        <v>99.89374023917654</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.79116927099179</v>
+        <v>87.61124090814697</v>
       </c>
       <c r="C8" t="n">
-        <v>42.9997533341249</v>
+        <v>42.7465373668299</v>
       </c>
       <c r="D8" t="n">
-        <v>1.995825300944374</v>
+        <v>1.977679320525282</v>
       </c>
       <c r="E8" t="n">
-        <v>9.524273738495515</v>
+        <v>9.538724813298018</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494023362867199</v>
+        <v>0.7494928365955407</v>
       </c>
       <c r="G8" t="n">
-        <v>30.82077635154592</v>
+        <v>30.57191928079047</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4725074691891</v>
+        <v>34.47667048339487</v>
       </c>
       <c r="I8" t="n">
-        <v>5.544619472738164</v>
+        <v>5.612423944820667</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683764601791999</v>
+        <v>4.684330228722129</v>
       </c>
       <c r="K8" t="n">
-        <v>12.20883072900821</v>
+        <v>12.38875909185302</v>
       </c>
       <c r="L8" t="n">
-        <v>44.60698356044368</v>
+        <v>44.67802137520723</v>
       </c>
       <c r="M8" t="n">
-        <v>99.8155676235768</v>
+        <v>99.81331783389015</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.66100814926482</v>
+        <v>85.41309687134508</v>
       </c>
       <c r="C9" t="n">
-        <v>41.73020264342585</v>
+        <v>41.41917554007696</v>
       </c>
       <c r="D9" t="n">
-        <v>1.898829789672178</v>
+        <v>1.877818693223856</v>
       </c>
       <c r="E9" t="n">
-        <v>9.832874797308465</v>
+        <v>9.838006668466289</v>
       </c>
       <c r="F9" t="n">
-        <v>0.75075217743906</v>
+        <v>0.7508633535364887</v>
       </c>
       <c r="G9" t="n">
-        <v>29.32291130363332</v>
+        <v>29.02822561645189</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53460016219675</v>
+        <v>34.53971426267848</v>
       </c>
       <c r="I9" t="n">
-        <v>4.628838810020929</v>
+        <v>4.685572317385027</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692201108994125</v>
+        <v>4.692895959603054</v>
       </c>
       <c r="K9" t="n">
-        <v>14.33899185073519</v>
+        <v>14.5869031286549</v>
       </c>
       <c r="L9" t="n">
-        <v>43.77678829826291</v>
+        <v>43.83802066613423</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84598279242394</v>
+        <v>99.8440993348661</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.33748913949428</v>
+        <v>83.15204949178955</v>
       </c>
       <c r="C10" t="n">
-        <v>40.12474333745205</v>
+        <v>39.88464088509314</v>
       </c>
       <c r="D10" t="n">
-        <v>1.794132101737707</v>
+        <v>1.776391679573114</v>
       </c>
       <c r="E10" t="n">
-        <v>9.934597403589684</v>
+        <v>9.95841851950825</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519122798326722</v>
+        <v>0.7520404943363687</v>
       </c>
       <c r="G10" t="n">
-        <v>27.7061044504356</v>
+        <v>27.46031799763808</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5879648723029</v>
+        <v>34.59386273947296</v>
       </c>
       <c r="I10" t="n">
-        <v>3.863326282641503</v>
+        <v>3.910764971658502</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699451748954201</v>
+        <v>4.700253089602303</v>
       </c>
       <c r="K10" t="n">
-        <v>16.66251086050573</v>
+        <v>16.84795050821043</v>
       </c>
       <c r="L10" t="n">
-        <v>43.08416694620831</v>
+        <v>43.13725382010239</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87142114416609</v>
+        <v>99.86984521340597</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.91738224953077</v>
+        <v>80.77130431511739</v>
       </c>
       <c r="C11" t="n">
-        <v>38.3032124404435</v>
+        <v>38.10958531600286</v>
       </c>
       <c r="D11" t="n">
-        <v>1.68626298156623</v>
+        <v>1.670739189134694</v>
       </c>
       <c r="E11" t="n">
-        <v>9.874582403904887</v>
+        <v>9.910025939010486</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529108086319817</v>
+        <v>0.7530533040038275</v>
       </c>
       <c r="G11" t="n">
-        <v>26.04032236696868</v>
+        <v>25.82709092387773</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63389719707114</v>
+        <v>34.64045198417607</v>
       </c>
       <c r="I11" t="n">
-        <v>3.223713937437958</v>
+        <v>3.26335982489067</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705692553949885</v>
+        <v>4.706583150023921</v>
       </c>
       <c r="K11" t="n">
-        <v>19.08261775046923</v>
+        <v>19.22869568488262</v>
       </c>
       <c r="L11" t="n">
-        <v>42.50685519012503</v>
+        <v>42.55308663879068</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89268538103777</v>
+        <v>99.89136763967616</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.437068683593</v>
+        <v>78.4108019236397</v>
       </c>
       <c r="C12" t="n">
-        <v>36.3215030420004</v>
+        <v>36.25365138467276</v>
       </c>
       <c r="D12" t="n">
-        <v>1.576830960254</v>
+        <v>1.567124283955685</v>
       </c>
       <c r="E12" t="n">
-        <v>9.682009544964261</v>
+        <v>9.749200880916698</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537713510213245</v>
+        <v>0.7539248988484462</v>
       </c>
       <c r="G12" t="n">
-        <v>24.35040499145192</v>
+        <v>24.22536182424895</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67348214698092</v>
+        <v>34.68054534702853</v>
       </c>
       <c r="I12" t="n">
-        <v>2.689498745037303</v>
+        <v>2.722614070838599</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711070943883278</v>
+        <v>4.712030617802788</v>
       </c>
       <c r="K12" t="n">
-        <v>21.56293131640699</v>
+        <v>21.5891980763603</v>
       </c>
       <c r="L12" t="n">
-        <v>42.02601803221933</v>
+        <v>42.06650165494221</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91045239062672</v>
+        <v>99.90935111597528</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.94449838731327</v>
+        <v>75.96286064805011</v>
       </c>
       <c r="C13" t="n">
-        <v>34.24398804377807</v>
+        <v>34.22581145555223</v>
       </c>
       <c r="D13" t="n">
-        <v>1.467900203974633</v>
+        <v>1.460642471378152</v>
       </c>
       <c r="E13" t="n">
-        <v>9.387065540783501</v>
+        <v>9.465287016046059</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545135828768068</v>
+        <v>0.754676249998368</v>
       </c>
       <c r="G13" t="n">
-        <v>22.668228462523</v>
+        <v>22.5793146895052</v>
       </c>
       <c r="H13" t="n">
-        <v>34.7076248123331</v>
+        <v>34.71510749992493</v>
       </c>
       <c r="I13" t="n">
-        <v>2.243455891842196</v>
+        <v>2.271106158707614</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715709892980041</v>
+        <v>4.716726562489799</v>
       </c>
       <c r="K13" t="n">
-        <v>24.05550161268672</v>
+        <v>24.03713935194988</v>
       </c>
       <c r="L13" t="n">
-        <v>41.62580204506195</v>
+        <v>41.66142102386348</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92529170152673</v>
+        <v>99.92437183136558</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.002314772982</v>
+        <v>82.97659298313074</v>
       </c>
       <c r="C14" t="n">
-        <v>38.71228804456146</v>
+        <v>38.58035140383694</v>
       </c>
       <c r="D14" t="n">
-        <v>1.469546075705447</v>
+        <v>1.462376540892532</v>
       </c>
       <c r="E14" t="n">
-        <v>11.85003121777012</v>
+        <v>11.88557804500704</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7553595753858411</v>
+        <v>0.7555721989413794</v>
       </c>
       <c r="G14" t="n">
-        <v>24.68075702873772</v>
+        <v>24.52262707410353</v>
       </c>
       <c r="H14" t="n">
-        <v>36.73365245842707</v>
+        <v>36.67282745431378</v>
       </c>
       <c r="I14" t="n">
-        <v>2.791971070794284</v>
+        <v>2.955285426488864</v>
       </c>
       <c r="J14" t="n">
-        <v>4.720997346161505</v>
+        <v>4.722326243383621</v>
       </c>
       <c r="K14" t="n">
-        <v>16.997685227018</v>
+        <v>17.02340701686927</v>
       </c>
       <c r="L14" t="n">
-        <v>44.19706525838876</v>
+        <v>44.29784887654205</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90703852996822</v>
+        <v>99.90160729724826</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.09870436851621</v>
+        <v>82.17942366475937</v>
       </c>
       <c r="C15" t="n">
-        <v>38.23985725296586</v>
+        <v>38.23944084980768</v>
       </c>
       <c r="D15" t="n">
-        <v>1.435958203595833</v>
+        <v>1.433025250736798</v>
       </c>
       <c r="E15" t="n">
-        <v>11.96732791055805</v>
+        <v>12.05788990728453</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7560738024454282</v>
+        <v>0.7563277152707423</v>
       </c>
       <c r="G15" t="n">
-        <v>24.11665487205526</v>
+        <v>24.03043458981108</v>
       </c>
       <c r="H15" t="n">
-        <v>36.76838580852709</v>
+        <v>36.70949757005449</v>
       </c>
       <c r="I15" t="n">
-        <v>2.328842506050614</v>
+        <v>2.46520041115958</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725461265283925</v>
+        <v>4.727048220442139</v>
       </c>
       <c r="K15" t="n">
-        <v>17.90129563148381</v>
+        <v>17.82057633524064</v>
       </c>
       <c r="L15" t="n">
-        <v>43.78129236358382</v>
+        <v>43.85789155310479</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92244524803348</v>
+        <v>99.9179087381531</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.47034977975255</v>
+        <v>79.55168757704941</v>
       </c>
       <c r="C16" t="n">
-        <v>35.9711105479535</v>
+        <v>35.99233032138758</v>
       </c>
       <c r="D16" t="n">
-        <v>1.336454059349516</v>
+        <v>1.333814205647028</v>
       </c>
       <c r="E16" t="n">
-        <v>11.46177060838487</v>
+        <v>11.56578333868963</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756689759382137</v>
+        <v>0.7569793201818904</v>
       </c>
       <c r="G16" t="n">
-        <v>22.44550100481982</v>
+        <v>22.36676220972517</v>
       </c>
       <c r="H16" t="n">
-        <v>36.79834021538142</v>
+        <v>36.74112418959978</v>
       </c>
       <c r="I16" t="n">
-        <v>1.942283136296434</v>
+        <v>2.056103562069085</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729310996138354</v>
+        <v>4.731120751136816</v>
       </c>
       <c r="K16" t="n">
-        <v>20.52965022024745</v>
+        <v>20.4483124229506</v>
       </c>
       <c r="L16" t="n">
-        <v>43.43454916218653</v>
+        <v>43.49087946646294</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93530993038749</v>
+        <v>99.93152221080112</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.16299081412151</v>
+        <v>81.29257169360504</v>
       </c>
       <c r="C17" t="n">
-        <v>37.20893231467586</v>
+        <v>37.25552542148571</v>
       </c>
       <c r="D17" t="n">
-        <v>1.337507662904092</v>
+        <v>1.334937030096281</v>
       </c>
       <c r="E17" t="n">
-        <v>12.23550502131262</v>
+        <v>12.36321460674865</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757286301414105</v>
+        <v>0.7576165565261134</v>
       </c>
       <c r="G17" t="n">
-        <v>22.90796726916401</v>
+        <v>22.83111947829606</v>
       </c>
       <c r="H17" t="n">
-        <v>37.27212164787875</v>
+        <v>37.21758200786124</v>
       </c>
       <c r="I17" t="n">
-        <v>1.919563527609774</v>
+        <v>2.052998535788488</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733039383838154</v>
+        <v>4.735103478288209</v>
       </c>
       <c r="K17" t="n">
-        <v>18.83700918587849</v>
+        <v>18.70742830639495</v>
       </c>
       <c r="L17" t="n">
-        <v>43.89012345219808</v>
+        <v>43.9686705472856</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93606495275242</v>
+        <v>99.93162427516626</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.67425056637882</v>
+        <v>78.91626119295269</v>
       </c>
       <c r="C18" t="n">
-        <v>35.01613205255348</v>
+        <v>35.19571585654093</v>
       </c>
       <c r="D18" t="n">
-        <v>1.247107827481436</v>
+        <v>1.248998972760821</v>
       </c>
       <c r="E18" t="n">
-        <v>11.67531520542463</v>
+        <v>11.85266379001041</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7577998977497955</v>
+        <v>0.7581644334952237</v>
       </c>
       <c r="G18" t="n">
-        <v>21.35965728303386</v>
+        <v>21.36134074677264</v>
       </c>
       <c r="H18" t="n">
-        <v>37.29739983535687</v>
+        <v>37.24449622436355</v>
       </c>
       <c r="I18" t="n">
-        <v>1.600721156396001</v>
+        <v>1.712069316204893</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73624936093622</v>
+        <v>4.738527709345147</v>
       </c>
       <c r="K18" t="n">
-        <v>21.32574943362119</v>
+        <v>21.08373880704731</v>
       </c>
       <c r="L18" t="n">
-        <v>43.60479730472505</v>
+        <v>43.66351759930652</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94667879089971</v>
+        <v>99.94297226289477</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.70307628490674</v>
+        <v>77.99750242141036</v>
       </c>
       <c r="C19" t="n">
-        <v>34.27998747128538</v>
+        <v>34.53872559121503</v>
       </c>
       <c r="D19" t="n">
-        <v>1.212011299211671</v>
+        <v>1.216382058660633</v>
       </c>
       <c r="E19" t="n">
-        <v>11.570977060606</v>
+        <v>11.78130808692746</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7582372636252022</v>
+        <v>0.7586274535577717</v>
       </c>
       <c r="G19" t="n">
-        <v>20.75854661790362</v>
+        <v>20.80350120374865</v>
       </c>
       <c r="H19" t="n">
-        <v>37.3189261115913</v>
+        <v>37.26724188244181</v>
       </c>
       <c r="I19" t="n">
-        <v>1.345395034311432</v>
+        <v>1.429020151337972</v>
       </c>
       <c r="J19" t="n">
-        <v>4.738982897657511</v>
+        <v>4.741421584736073</v>
       </c>
       <c r="K19" t="n">
-        <v>22.29692371509326</v>
+        <v>22.00249757858965</v>
       </c>
       <c r="L19" t="n">
-        <v>43.37826818080431</v>
+        <v>43.4111718980506</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95517936718295</v>
+        <v>99.95239506785526</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.14522099878502</v>
+        <v>75.40426494802762</v>
       </c>
       <c r="C20" t="n">
-        <v>31.92877737665695</v>
+        <v>32.16505635053094</v>
       </c>
       <c r="D20" t="n">
-        <v>1.120141200170534</v>
+        <v>1.123652388015226</v>
       </c>
       <c r="E20" t="n">
-        <v>10.88085381109893</v>
+        <v>11.08175139771147</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7586145465235256</v>
+        <v>0.7590270275217784</v>
       </c>
       <c r="G20" t="n">
-        <v>19.18505490625267</v>
+        <v>19.21756707954831</v>
       </c>
       <c r="H20" t="n">
-        <v>37.33749522350541</v>
+        <v>37.28687077867635</v>
       </c>
       <c r="I20" t="n">
-        <v>1.121720395461941</v>
+        <v>1.191477354543368</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741340915772033</v>
+        <v>4.743918922011114</v>
       </c>
       <c r="K20" t="n">
-        <v>24.85477900121495</v>
+        <v>24.59573505197238</v>
       </c>
       <c r="L20" t="n">
-        <v>43.17907153784168</v>
+        <v>43.19951359329286</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96262791571358</v>
+        <v>99.96030499579618</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.25583469451213</v>
+        <v>81.40338155698339</v>
       </c>
       <c r="C21" t="n">
-        <v>35.8010958480499</v>
+        <v>35.90843795247223</v>
       </c>
       <c r="D21" t="n">
-        <v>1.120841879995869</v>
+        <v>1.124428309645821</v>
       </c>
       <c r="E21" t="n">
-        <v>12.94415146126131</v>
+        <v>13.09444015694781</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7590890812588549</v>
+        <v>0.759551162472358</v>
       </c>
       <c r="G21" t="n">
-        <v>20.99940801791364</v>
+        <v>20.95481436711638</v>
       </c>
       <c r="H21" t="n">
-        <v>39.16320319713284</v>
+        <v>39.0365955581623</v>
       </c>
       <c r="I21" t="n">
-        <v>1.524834299081786</v>
+        <v>1.686357237186485</v>
       </c>
       <c r="J21" t="n">
-        <v>4.74430675786784</v>
+        <v>4.747194765452237</v>
       </c>
       <c r="K21" t="n">
-        <v>18.74416530548786</v>
+        <v>18.59661844301661</v>
       </c>
       <c r="L21" t="n">
-        <v>45.40394281084178</v>
+        <v>45.43877048612569</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94920396437955</v>
+        <v>99.94382688161453</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_55_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_55_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.42922771489483</v>
+        <v>45.71650625042452</v>
       </c>
       <c r="M2" t="n">
-        <v>99.84962337665087</v>
+        <v>99.05750972416379</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.0459273450542</v>
+        <v>88.08013143507013</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93012358362086</v>
+        <v>45.94971081385907</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228777275087503</v>
+        <v>2.228850104535375</v>
       </c>
       <c r="E3" t="n">
-        <v>5.708212956870103</v>
+        <v>5.721256239439724</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742925758362501</v>
+        <v>0.7429500348451251</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97342387848605</v>
+        <v>33.97986768402979</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17458488467504</v>
+        <v>34.17570160287575</v>
       </c>
       <c r="I3" t="n">
-        <v>6.574716601807366</v>
+        <v>6.588068051562335</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643285989765631</v>
+        <v>4.643437717782032</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95407265494581</v>
+        <v>11.91986856492985</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87981009170966</v>
+        <v>48.89395543988169</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7640063302763</v>
+        <v>106.7635348186706</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.08963295243207</v>
+        <v>87.21585815297431</v>
       </c>
       <c r="C4" t="n">
-        <v>42.6102005597684</v>
+        <v>42.72366023236004</v>
       </c>
       <c r="D4" t="n">
-        <v>2.182498764056086</v>
+        <v>2.187498322208531</v>
       </c>
       <c r="E4" t="n">
-        <v>6.504761199279031</v>
+        <v>6.532043381452648</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444869822405867</v>
+        <v>0.744512217986404</v>
       </c>
       <c r="G4" t="n">
-        <v>33.26799696602177</v>
+        <v>33.34944032190896</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24640118306699</v>
+        <v>34.24756202737458</v>
       </c>
       <c r="I4" t="n">
-        <v>5.49044421876394</v>
+        <v>5.501600519628161</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653043639003667</v>
+        <v>4.653201362415024</v>
       </c>
       <c r="K4" t="n">
-        <v>12.91036704756793</v>
+        <v>12.7841418470257</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29680137594681</v>
+        <v>44.30919603029307</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81736898328315</v>
+        <v>99.81699810967879</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.8938595389632</v>
+        <v>86.08800713418108</v>
       </c>
       <c r="C5" t="n">
-        <v>42.26653219517915</v>
+        <v>42.44975440804501</v>
       </c>
       <c r="D5" t="n">
-        <v>2.124066494337297</v>
+        <v>2.132638278298223</v>
       </c>
       <c r="E5" t="n">
-        <v>7.094526644214809</v>
+        <v>7.133696976947787</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458112377489312</v>
+        <v>0.7458362160962159</v>
       </c>
       <c r="G5" t="n">
-        <v>32.37730937263697</v>
+        <v>32.51307316136322</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30731693645083</v>
+        <v>34.30846594042593</v>
       </c>
       <c r="I5" t="n">
-        <v>4.583508617643543</v>
+        <v>4.592820210448374</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661320235930821</v>
+        <v>4.661476350601348</v>
       </c>
       <c r="K5" t="n">
-        <v>14.1061404610368</v>
+        <v>13.91199286581892</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47481500437394</v>
+        <v>43.48543048947975</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84748766058989</v>
+        <v>99.84717776334367</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.54315263032525</v>
+        <v>84.80007636539814</v>
       </c>
       <c r="C6" t="n">
-        <v>41.62760525941723</v>
+        <v>41.87520555981808</v>
       </c>
       <c r="D6" t="n">
-        <v>2.058193146737294</v>
+        <v>2.070009841413125</v>
       </c>
       <c r="E6" t="n">
-        <v>7.512063745167559</v>
+        <v>7.563057035917912</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469361031641943</v>
+        <v>0.7469599876627491</v>
       </c>
       <c r="G6" t="n">
-        <v>31.37319685528285</v>
+        <v>31.55827319779328</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35906074555294</v>
+        <v>34.36015943248645</v>
       </c>
       <c r="I6" t="n">
-        <v>3.82535138964421</v>
+        <v>3.833116947232436</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668350644776215</v>
+        <v>4.668499922892181</v>
       </c>
       <c r="K6" t="n">
-        <v>15.45684736967473</v>
+        <v>15.19992363460188</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78822768708461</v>
+        <v>42.79729246640092</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87268031617657</v>
+        <v>99.87242166082088</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.80729214808186</v>
+        <v>83.27575026247237</v>
       </c>
       <c r="C7" t="n">
-        <v>40.48582817222574</v>
+        <v>40.9463513136436</v>
       </c>
       <c r="D7" t="n">
-        <v>1.973465278404667</v>
+        <v>1.995959100425643</v>
       </c>
       <c r="E7" t="n">
-        <v>7.734802525294923</v>
+        <v>7.825561694591952</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478958161131329</v>
+        <v>0.747916265284765</v>
       </c>
       <c r="G7" t="n">
-        <v>30.08168342441664</v>
+        <v>30.42933483826033</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40320754120411</v>
+        <v>34.40414820309919</v>
       </c>
       <c r="I7" t="n">
-        <v>3.191888711941308</v>
+        <v>3.198353502780705</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674348850707081</v>
+        <v>4.67447665802978</v>
       </c>
       <c r="K7" t="n">
-        <v>17.19270785191814</v>
+        <v>16.72424973752763</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21520421503266</v>
+        <v>42.22292347807233</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89374023917654</v>
+        <v>99.89352452924356</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.61124090814697</v>
+        <v>88.07077304860259</v>
       </c>
       <c r="C8" t="n">
-        <v>42.7465373668299</v>
+        <v>43.16892620312018</v>
       </c>
       <c r="D8" t="n">
-        <v>1.977679320525282</v>
+        <v>2.000225374737012</v>
       </c>
       <c r="E8" t="n">
-        <v>9.538724813298018</v>
+        <v>9.605896066766773</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494928365955407</v>
+        <v>0.7495149032272755</v>
       </c>
       <c r="G8" t="n">
-        <v>30.57191928079047</v>
+        <v>30.9055615291215</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47667048339487</v>
+        <v>34.47768554845468</v>
       </c>
       <c r="I8" t="n">
-        <v>5.612423944820667</v>
+        <v>5.647421481124882</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684330228722129</v>
+        <v>4.684468145170472</v>
       </c>
       <c r="K8" t="n">
-        <v>12.38875909185302</v>
+        <v>11.92922695139741</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67802137520723</v>
+        <v>44.71400097501939</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81331783389015</v>
+        <v>99.81215412953698</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.41309687134508</v>
+        <v>86.04703571219854</v>
       </c>
       <c r="C9" t="n">
-        <v>41.41917554007696</v>
+        <v>42.02182463204917</v>
       </c>
       <c r="D9" t="n">
-        <v>1.877818693223856</v>
+        <v>1.908485490232766</v>
       </c>
       <c r="E9" t="n">
-        <v>9.838006668466289</v>
+        <v>9.951120500643531</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508633535364887</v>
+        <v>0.750883843647589</v>
       </c>
       <c r="G9" t="n">
-        <v>29.02822561645189</v>
+        <v>29.48808493821821</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53971426267848</v>
+        <v>34.5406568077891</v>
       </c>
       <c r="I9" t="n">
-        <v>4.685572317385027</v>
+        <v>4.714780108869904</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692895959603054</v>
+        <v>4.693024022797431</v>
       </c>
       <c r="K9" t="n">
-        <v>14.5869031286549</v>
+        <v>13.95296428780148</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83802066613423</v>
+        <v>43.86833826122922</v>
       </c>
       <c r="M9" t="n">
-        <v>99.8440993348661</v>
+        <v>99.84312718107986</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.15204949178955</v>
+        <v>83.72809177779214</v>
       </c>
       <c r="C10" t="n">
-        <v>39.88464088509314</v>
+        <v>40.43446140901207</v>
       </c>
       <c r="D10" t="n">
-        <v>1.776391679573114</v>
+        <v>1.804272201440498</v>
       </c>
       <c r="E10" t="n">
-        <v>9.95841851950825</v>
+        <v>10.06359372941998</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520404943363687</v>
+        <v>0.7520602039397496</v>
       </c>
       <c r="G10" t="n">
-        <v>27.46031799763808</v>
+        <v>27.87788128337006</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59386273947296</v>
+        <v>34.59476938122849</v>
       </c>
       <c r="I10" t="n">
-        <v>3.910764971658502</v>
+        <v>3.935138703769916</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700253089602303</v>
+        <v>4.700376274623435</v>
       </c>
       <c r="K10" t="n">
-        <v>16.84795050821043</v>
+        <v>16.27190822220788</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13725382010239</v>
+        <v>43.16266425464478</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86984521340597</v>
+        <v>99.86903388586472</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.77130431511739</v>
+        <v>81.31430615560544</v>
       </c>
       <c r="C11" t="n">
-        <v>38.10958531600286</v>
+        <v>38.6305688381739</v>
       </c>
       <c r="D11" t="n">
-        <v>1.670739189134694</v>
+        <v>1.6969787715555</v>
       </c>
       <c r="E11" t="n">
-        <v>9.910025939010486</v>
+        <v>10.01243157926072</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530533040038275</v>
+        <v>0.7530725462745247</v>
       </c>
       <c r="G11" t="n">
-        <v>25.82709092387773</v>
+        <v>26.22008624643964</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64045198417607</v>
+        <v>34.64133712862814</v>
       </c>
       <c r="I11" t="n">
-        <v>3.26335982489067</v>
+        <v>3.283696469231135</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706583150023921</v>
+        <v>4.70670341421578</v>
       </c>
       <c r="K11" t="n">
-        <v>19.22869568488262</v>
+        <v>18.68569384439455</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55308663879068</v>
+        <v>42.57442790899352</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89136763967616</v>
+        <v>99.89069059156198</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.4108019236397</v>
+        <v>78.76435492650548</v>
       </c>
       <c r="C12" t="n">
-        <v>36.25365138467276</v>
+        <v>36.58868686849026</v>
       </c>
       <c r="D12" t="n">
-        <v>1.567124283955685</v>
+        <v>1.584728282553484</v>
       </c>
       <c r="E12" t="n">
-        <v>9.749200880916698</v>
+        <v>9.806734427022478</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539248988484462</v>
+        <v>0.7539456600298744</v>
       </c>
       <c r="G12" t="n">
-        <v>24.22536182424895</v>
+        <v>24.48569949265601</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68054534702853</v>
+        <v>34.68150036137423</v>
       </c>
       <c r="I12" t="n">
-        <v>2.722614070838599</v>
+        <v>2.739586327682671</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712030617802788</v>
+        <v>4.712160375186715</v>
       </c>
       <c r="K12" t="n">
-        <v>21.5891980763603</v>
+        <v>21.23564507349455</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06650165494221</v>
+        <v>42.08445426720321</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90935111597528</v>
+        <v>99.90878620918801</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.96286064805011</v>
+        <v>76.24662239308782</v>
       </c>
       <c r="C13" t="n">
-        <v>34.22581145555223</v>
+        <v>34.49387342991125</v>
       </c>
       <c r="D13" t="n">
-        <v>1.460642471378152</v>
+        <v>1.474989794621495</v>
       </c>
       <c r="E13" t="n">
-        <v>9.465287016046059</v>
+        <v>9.508520729609948</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754676249998368</v>
+        <v>0.7546989038872245</v>
       </c>
       <c r="G13" t="n">
-        <v>22.5793146895052</v>
+        <v>22.79012576694985</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71510749992493</v>
+        <v>34.71614957881233</v>
       </c>
       <c r="I13" t="n">
-        <v>2.271106158707614</v>
+        <v>2.285269469911812</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716726562489799</v>
+        <v>4.716868149295153</v>
       </c>
       <c r="K13" t="n">
-        <v>24.03713935194988</v>
+        <v>23.75337760691218</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66142102386348</v>
+        <v>41.67664934296317</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92437183136558</v>
+        <v>99.9239003797866</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.97659298313074</v>
+        <v>83.15131462205552</v>
       </c>
       <c r="C14" t="n">
-        <v>38.58035140383694</v>
+        <v>38.70412814586412</v>
       </c>
       <c r="D14" t="n">
-        <v>1.462376540892532</v>
+        <v>1.476813381133008</v>
       </c>
       <c r="E14" t="n">
-        <v>11.88557804500704</v>
+        <v>11.86776220743063</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555721989413794</v>
+        <v>0.7556319671168148</v>
       </c>
       <c r="G14" t="n">
-        <v>24.52262707410353</v>
+        <v>24.6517719897554</v>
       </c>
       <c r="H14" t="n">
-        <v>36.67282745431378</v>
+        <v>36.59254040272536</v>
       </c>
       <c r="I14" t="n">
-        <v>2.955285426488864</v>
+        <v>3.084094879414227</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722326243383621</v>
+        <v>4.722699794480092</v>
       </c>
       <c r="K14" t="n">
-        <v>17.02340701686927</v>
+        <v>16.84868537794446</v>
       </c>
       <c r="L14" t="n">
-        <v>44.29784887654205</v>
+        <v>44.34451025609717</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90160729724826</v>
+        <v>99.89732377990575</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.17942366475937</v>
+        <v>82.2444153627805</v>
       </c>
       <c r="C15" t="n">
-        <v>38.23944084980768</v>
+        <v>38.27342679719057</v>
       </c>
       <c r="D15" t="n">
-        <v>1.433025250736798</v>
+        <v>1.443067865936393</v>
       </c>
       <c r="E15" t="n">
-        <v>12.05788990728453</v>
+        <v>12.02537435394245</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563277152707423</v>
+        <v>0.7564198864370498</v>
       </c>
       <c r="G15" t="n">
-        <v>24.03043458981108</v>
+        <v>24.08847350063583</v>
       </c>
       <c r="H15" t="n">
-        <v>36.70949757005449</v>
+        <v>36.63069650359785</v>
       </c>
       <c r="I15" t="n">
-        <v>2.46520041115958</v>
+        <v>2.572758961999368</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727048220442139</v>
+        <v>4.72762429023156</v>
       </c>
       <c r="K15" t="n">
-        <v>17.82057633524064</v>
+        <v>17.7555846372195</v>
       </c>
       <c r="L15" t="n">
-        <v>43.85789155310479</v>
+        <v>43.88531926338398</v>
       </c>
       <c r="M15" t="n">
-        <v>99.9179087381531</v>
+        <v>99.91433069779404</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.55168757704941</v>
+        <v>79.69100739375908</v>
       </c>
       <c r="C16" t="n">
-        <v>35.99233032138758</v>
+        <v>36.1172552715413</v>
       </c>
       <c r="D16" t="n">
-        <v>1.333814205647028</v>
+        <v>1.346164231194144</v>
       </c>
       <c r="E16" t="n">
-        <v>11.56578333868963</v>
+        <v>11.57550526994246</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569793201818904</v>
+        <v>0.7570988396731494</v>
       </c>
       <c r="G16" t="n">
-        <v>22.36676220972517</v>
+        <v>22.47090533720834</v>
       </c>
       <c r="H16" t="n">
-        <v>36.74112418959978</v>
+        <v>36.66357576864316</v>
       </c>
       <c r="I16" t="n">
-        <v>2.056103562069085</v>
+        <v>2.145890199140649</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731120751136816</v>
+        <v>4.731867747957183</v>
       </c>
       <c r="K16" t="n">
-        <v>20.4483124229506</v>
+        <v>20.30899260624094</v>
       </c>
       <c r="L16" t="n">
-        <v>43.49087946646294</v>
+        <v>43.50228659549555</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93152221080112</v>
+        <v>99.92853447327778</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.29257169360504</v>
+        <v>81.33234229310409</v>
       </c>
       <c r="C17" t="n">
-        <v>37.25552542148571</v>
+        <v>37.30241971686382</v>
       </c>
       <c r="D17" t="n">
-        <v>1.334937030096281</v>
+        <v>1.347360540364033</v>
       </c>
       <c r="E17" t="n">
-        <v>12.36321460674865</v>
+        <v>12.34337347597771</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576165565261134</v>
+        <v>0.757771658236758</v>
       </c>
       <c r="G17" t="n">
-        <v>22.83111947829606</v>
+        <v>22.88706395500195</v>
       </c>
       <c r="H17" t="n">
-        <v>37.21758200786124</v>
+        <v>37.0923471281728</v>
       </c>
       <c r="I17" t="n">
-        <v>2.052998535788488</v>
+        <v>2.168352671371113</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735103478288209</v>
+        <v>4.736072863979736</v>
       </c>
       <c r="K17" t="n">
-        <v>18.70742830639495</v>
+        <v>18.66765770689591</v>
       </c>
       <c r="L17" t="n">
-        <v>43.9686705472856</v>
+        <v>43.95770832921512</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93162427516626</v>
+        <v>99.92778575297486</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.91626119295269</v>
+        <v>78.91168624865092</v>
       </c>
       <c r="C18" t="n">
-        <v>35.19571585654093</v>
+        <v>35.21607367837325</v>
       </c>
       <c r="D18" t="n">
-        <v>1.248998972760821</v>
+        <v>1.259155619831495</v>
       </c>
       <c r="E18" t="n">
-        <v>11.85266379001041</v>
+        <v>11.83670501203933</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581644334952237</v>
+        <v>0.758350494950633</v>
       </c>
       <c r="G18" t="n">
-        <v>21.36134074677264</v>
+        <v>21.38876294580908</v>
       </c>
       <c r="H18" t="n">
-        <v>37.24449622436355</v>
+        <v>37.12068074567908</v>
       </c>
       <c r="I18" t="n">
-        <v>1.712069316204893</v>
+        <v>1.808340836899845</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738527709345147</v>
+        <v>4.739690593441455</v>
       </c>
       <c r="K18" t="n">
-        <v>21.08373880704731</v>
+        <v>21.0883137513491</v>
       </c>
       <c r="L18" t="n">
-        <v>43.66351759930652</v>
+        <v>43.63538055162846</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94297226289477</v>
+        <v>99.9397679813508</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.99750242141036</v>
+        <v>77.9703276449568</v>
       </c>
       <c r="C19" t="n">
-        <v>34.53872559121503</v>
+        <v>34.55190316283374</v>
       </c>
       <c r="D19" t="n">
-        <v>1.216382058660633</v>
+        <v>1.225536346402901</v>
       </c>
       <c r="E19" t="n">
-        <v>11.78130808692746</v>
+        <v>11.77212768167195</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586274535577717</v>
+        <v>0.7588396440129708</v>
       </c>
       <c r="G19" t="n">
-        <v>20.80350120374865</v>
+        <v>20.81768606027626</v>
       </c>
       <c r="H19" t="n">
-        <v>37.26724188244181</v>
+        <v>37.14462422076215</v>
       </c>
       <c r="I19" t="n">
-        <v>1.429020151337972</v>
+        <v>1.508765916749494</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741421584736073</v>
+        <v>4.742747775081066</v>
       </c>
       <c r="K19" t="n">
-        <v>22.00249757858965</v>
+        <v>22.0296723550432</v>
       </c>
       <c r="L19" t="n">
-        <v>43.4111718980506</v>
+        <v>43.36816470331655</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95239506785526</v>
+        <v>99.94974022119348</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.40426494802762</v>
+        <v>75.42075830945896</v>
       </c>
       <c r="C20" t="n">
-        <v>32.16505635053094</v>
+        <v>32.234171218637</v>
       </c>
       <c r="D20" t="n">
-        <v>1.123652388015226</v>
+        <v>1.133764838055679</v>
       </c>
       <c r="E20" t="n">
-        <v>11.08175139771147</v>
+        <v>11.10026594392286</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590270275217784</v>
+        <v>0.7592615540710526</v>
       </c>
       <c r="G20" t="n">
-        <v>19.21756707954831</v>
+        <v>19.25880087856952</v>
       </c>
       <c r="H20" t="n">
-        <v>37.28687077867635</v>
+        <v>37.16527639765625</v>
       </c>
       <c r="I20" t="n">
-        <v>1.191477354543368</v>
+        <v>1.258003984239517</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743918922011114</v>
+        <v>4.745384712944077</v>
       </c>
       <c r="K20" t="n">
-        <v>24.59573505197238</v>
+        <v>24.57924169054104</v>
       </c>
       <c r="L20" t="n">
-        <v>43.19951359329286</v>
+        <v>43.1446769264678</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96030499579618</v>
+        <v>99.95808983564584</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.40338155698339</v>
+        <v>81.42300669359126</v>
       </c>
       <c r="C21" t="n">
-        <v>35.90843795247223</v>
+        <v>35.92921210612396</v>
       </c>
       <c r="D21" t="n">
-        <v>1.124428309645821</v>
+        <v>1.134617834092996</v>
       </c>
       <c r="E21" t="n">
-        <v>13.09444015694781</v>
+        <v>13.10170795202552</v>
       </c>
       <c r="F21" t="n">
-        <v>0.759551162472358</v>
+        <v>0.7598327898998337</v>
       </c>
       <c r="G21" t="n">
-        <v>20.95481436711638</v>
+        <v>20.96008512830105</v>
       </c>
       <c r="H21" t="n">
-        <v>39.0365955581623</v>
+        <v>38.88003271156494</v>
       </c>
       <c r="I21" t="n">
-        <v>1.686357237186485</v>
+        <v>1.837775340832978</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747194765452237</v>
+        <v>4.748954936873959</v>
       </c>
       <c r="K21" t="n">
-        <v>18.59661844301661</v>
+        <v>18.57699330640872</v>
       </c>
       <c r="L21" t="n">
-        <v>45.43877048612569</v>
+        <v>45.43258146356857</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94382688161453</v>
+        <v>99.93878687610125</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_55_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_55_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.71650625042452</v>
+        <v>43.51605978711916</v>
       </c>
       <c r="M2" t="n">
-        <v>99.05750972416379</v>
+        <v>96.85371172599145</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.08013143507013</v>
+        <v>81.50301481771288</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94971081385907</v>
+        <v>43.25857037326846</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228850104535375</v>
+        <v>2.180904291200535</v>
       </c>
       <c r="E3" t="n">
-        <v>5.721256239439724</v>
+        <v>4.164190377901127</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429500348451251</v>
+        <v>0.7376514038049901</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97986768402979</v>
+        <v>32.80443538014138</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17570160287575</v>
+        <v>33.93196457502954</v>
       </c>
       <c r="I3" t="n">
-        <v>6.588068051562335</v>
+        <v>3.073547515854125</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643437717782032</v>
+        <v>4.610321273781188</v>
       </c>
       <c r="K3" t="n">
-        <v>11.91986856492985</v>
+        <v>18.4969851822871</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89395543988169</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7635348186706</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.21585815297431</v>
+        <v>88.75101554086005</v>
       </c>
       <c r="C4" t="n">
-        <v>42.72366023236004</v>
+        <v>42.90470693147351</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187498322208531</v>
+        <v>2.186709504552155</v>
       </c>
       <c r="E4" t="n">
-        <v>6.532043381452648</v>
+        <v>6.586047875945288</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744512217986404</v>
+        <v>0.73961491215127</v>
       </c>
       <c r="G4" t="n">
-        <v>33.34944032190896</v>
+        <v>33.50654000699748</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24756202737458</v>
+        <v>34.02228595895841</v>
       </c>
       <c r="I4" t="n">
-        <v>5.501600519628161</v>
+        <v>7.087224081310021</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653201362415024</v>
+        <v>4.622593200945437</v>
       </c>
       <c r="K4" t="n">
-        <v>12.7841418470257</v>
+        <v>11.24898445913993</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30919603029307</v>
+        <v>45.61069497194862</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81699810967879</v>
+        <v>99.76438636256206</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.08800713418108</v>
+        <v>87.78248451769139</v>
       </c>
       <c r="C5" t="n">
-        <v>42.44975440804501</v>
+        <v>43.03471795443721</v>
       </c>
       <c r="D5" t="n">
-        <v>2.132638278298223</v>
+        <v>2.14141902552794</v>
       </c>
       <c r="E5" t="n">
-        <v>7.133696976947787</v>
+        <v>7.43618878909055</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458362160962159</v>
+        <v>0.7412773542485446</v>
       </c>
       <c r="G5" t="n">
-        <v>32.51307316136322</v>
+        <v>32.81256248314173</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30846594042593</v>
+        <v>34.09875829543304</v>
       </c>
       <c r="I5" t="n">
-        <v>4.592820210448374</v>
+        <v>5.919295106196167</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661476350601348</v>
+        <v>4.632983464053403</v>
       </c>
       <c r="K5" t="n">
-        <v>13.91199286581892</v>
+        <v>12.21751548230863</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48543048947975</v>
+        <v>44.5508992276622</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84717776334367</v>
+        <v>99.80313266440804</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.80007636539814</v>
+        <v>86.65178147457412</v>
       </c>
       <c r="C6" t="n">
-        <v>41.87520555981808</v>
+        <v>42.82286892919652</v>
       </c>
       <c r="D6" t="n">
-        <v>2.070009841413125</v>
+        <v>2.088261990845526</v>
       </c>
       <c r="E6" t="n">
-        <v>7.563057035917912</v>
+        <v>8.075285521738735</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469599876627491</v>
+        <v>0.7426866287712094</v>
       </c>
       <c r="G6" t="n">
-        <v>31.55827319779328</v>
+        <v>31.9980472009189</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36015943248645</v>
+        <v>34.16358492347563</v>
       </c>
       <c r="I6" t="n">
-        <v>3.833116947232436</v>
+        <v>4.942123779004072</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668499922892181</v>
+        <v>4.641791429820058</v>
       </c>
       <c r="K6" t="n">
-        <v>15.19992363460188</v>
+        <v>13.34821852542589</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79729246640092</v>
+        <v>43.66448768131659</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87242166082088</v>
+        <v>99.835575135939</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.27575026247237</v>
+        <v>85.36673998162661</v>
       </c>
       <c r="C7" t="n">
-        <v>40.9463513136436</v>
+        <v>42.3056459297441</v>
       </c>
       <c r="D7" t="n">
-        <v>1.995959100425643</v>
+        <v>2.027875036616</v>
       </c>
       <c r="E7" t="n">
-        <v>7.825561694591952</v>
+        <v>8.529281543911104</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747916265284765</v>
+        <v>0.7438828926574683</v>
       </c>
       <c r="G7" t="n">
-        <v>30.42933483826033</v>
+        <v>31.07274921617046</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40414820309919</v>
+        <v>34.21861306224354</v>
       </c>
       <c r="I7" t="n">
-        <v>3.198353502780705</v>
+        <v>4.125070150918862</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67447665802978</v>
+        <v>4.649268079109177</v>
       </c>
       <c r="K7" t="n">
-        <v>16.72424973752763</v>
+        <v>14.63326001837339</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22292347807233</v>
+        <v>42.92381283579908</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89352452924356</v>
+        <v>99.86271878391656</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.07077304860259</v>
+        <v>84.00950581157812</v>
       </c>
       <c r="C8" t="n">
-        <v>43.16892620312018</v>
+        <v>41.58948092915639</v>
       </c>
       <c r="D8" t="n">
-        <v>2.000225374737012</v>
+        <v>1.964440887419675</v>
       </c>
       <c r="E8" t="n">
-        <v>9.605896066766773</v>
+        <v>8.836185211715968</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495149032272755</v>
+        <v>0.7448989020948659</v>
       </c>
       <c r="G8" t="n">
-        <v>30.9055615291215</v>
+        <v>30.10075963390914</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47768554845468</v>
+        <v>34.26534949636383</v>
       </c>
       <c r="I8" t="n">
-        <v>5.647421481124882</v>
+        <v>3.442253541981753</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684468145170472</v>
+        <v>4.655618138092912</v>
       </c>
       <c r="K8" t="n">
-        <v>11.92922695139741</v>
+        <v>15.99049418842187</v>
       </c>
       <c r="L8" t="n">
-        <v>44.71400097501939</v>
+        <v>42.30543960045177</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81215412953698</v>
+        <v>99.88541471803003</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.04703571219854</v>
+        <v>82.30910283008336</v>
       </c>
       <c r="C9" t="n">
-        <v>42.02182463204917</v>
+        <v>40.42397242336457</v>
       </c>
       <c r="D9" t="n">
-        <v>1.908485490232766</v>
+        <v>1.884962475184794</v>
       </c>
       <c r="E9" t="n">
-        <v>9.951120500643531</v>
+        <v>8.95733286162034</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750883843647589</v>
+        <v>0.7457652545937745</v>
       </c>
       <c r="G9" t="n">
-        <v>29.48808493821821</v>
+        <v>28.88292681537658</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5406568077891</v>
+        <v>34.30520171131362</v>
       </c>
       <c r="I9" t="n">
-        <v>4.714780108869904</v>
+        <v>2.871880870783156</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693024022797431</v>
+        <v>4.661032841211091</v>
       </c>
       <c r="K9" t="n">
-        <v>13.95296428780148</v>
+        <v>17.69089716991663</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86833826122922</v>
+        <v>41.78951225277486</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84312718107986</v>
+        <v>99.90438184605608</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.72809177779214</v>
+        <v>86.47831032959233</v>
       </c>
       <c r="C10" t="n">
-        <v>40.43446140901207</v>
+        <v>43.3842856582225</v>
       </c>
       <c r="D10" t="n">
-        <v>1.804272201440498</v>
+        <v>1.887007593342451</v>
       </c>
       <c r="E10" t="n">
-        <v>10.06359372941998</v>
+        <v>10.6598456246859</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520602039397496</v>
+        <v>0.7465743837322047</v>
       </c>
       <c r="G10" t="n">
-        <v>27.87788128337006</v>
+        <v>30.13792848440132</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59476938122849</v>
+        <v>35.56608635837717</v>
       </c>
       <c r="I10" t="n">
-        <v>3.935138703769916</v>
+        <v>2.81477798672701</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700376274623435</v>
+        <v>4.66608989832628</v>
       </c>
       <c r="K10" t="n">
-        <v>16.27190822220788</v>
+        <v>13.52168967040766</v>
       </c>
       <c r="L10" t="n">
-        <v>43.16266425464478</v>
+        <v>43.00030042599715</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86903388586472</v>
+        <v>99.9062757546273</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.31430615560544</v>
+        <v>86.33280550234592</v>
       </c>
       <c r="C11" t="n">
-        <v>38.6305688381739</v>
+        <v>43.58709663050084</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6969787715555</v>
+        <v>1.876563447014663</v>
       </c>
       <c r="E11" t="n">
-        <v>10.01243157926072</v>
+        <v>11.0186057551417</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530725462745247</v>
+        <v>0.7472722217997613</v>
       </c>
       <c r="G11" t="n">
-        <v>26.22008624643964</v>
+        <v>29.98539694098647</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64133712862814</v>
+        <v>35.61360554563811</v>
       </c>
       <c r="I11" t="n">
-        <v>3.283696469231135</v>
+        <v>2.420910205516717</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70670341421578</v>
+        <v>4.670451386248508</v>
       </c>
       <c r="K11" t="n">
-        <v>18.68569384439455</v>
+        <v>13.66719449765408</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57442790899352</v>
+        <v>42.66508722366794</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89069059156198</v>
+        <v>99.91937835182286</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.76435492650548</v>
+        <v>84.6000698917355</v>
       </c>
       <c r="C12" t="n">
-        <v>36.58868686849026</v>
+        <v>42.23134028287616</v>
       </c>
       <c r="D12" t="n">
-        <v>1.584728282553484</v>
+        <v>1.80216701626244</v>
       </c>
       <c r="E12" t="n">
-        <v>9.806734427022478</v>
+        <v>10.91827771400316</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539456600298744</v>
+        <v>0.7478666913984697</v>
       </c>
       <c r="G12" t="n">
-        <v>24.48569949265601</v>
+        <v>28.7966247144748</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68150036137423</v>
+        <v>35.64193686209771</v>
       </c>
       <c r="I12" t="n">
-        <v>2.739586327682671</v>
+        <v>2.019030072258507</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712160375186715</v>
+        <v>4.674166821240435</v>
       </c>
       <c r="K12" t="n">
-        <v>21.23564507349455</v>
+        <v>15.39993010826449</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08445426720321</v>
+        <v>42.30148210315055</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90878620918801</v>
+        <v>99.93275249429119</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.24662239308782</v>
+        <v>85.66050467447774</v>
       </c>
       <c r="C13" t="n">
-        <v>34.49387342991125</v>
+        <v>43.15045145015902</v>
       </c>
       <c r="D13" t="n">
-        <v>1.474989794621495</v>
+        <v>1.803460660685015</v>
       </c>
       <c r="E13" t="n">
-        <v>9.508520729609948</v>
+        <v>11.52291422168441</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546989038872245</v>
+        <v>0.748403530418065</v>
       </c>
       <c r="G13" t="n">
-        <v>22.79012576694985</v>
+        <v>29.10664760318389</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71614957881233</v>
+        <v>35.95687350175255</v>
       </c>
       <c r="I13" t="n">
-        <v>2.285269469911812</v>
+        <v>1.844683091640891</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716868149295153</v>
+        <v>4.677522065112905</v>
       </c>
       <c r="K13" t="n">
-        <v>23.75337760691218</v>
+        <v>14.33949532552229</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67664934296317</v>
+        <v>42.44860789505657</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9239003797866</v>
+        <v>99.93855467073787</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.15131462205552</v>
+        <v>83.81909941048423</v>
       </c>
       <c r="C14" t="n">
-        <v>38.70412814586412</v>
+        <v>41.59622673692802</v>
       </c>
       <c r="D14" t="n">
-        <v>1.476813381133008</v>
+        <v>1.726253766613419</v>
       </c>
       <c r="E14" t="n">
-        <v>11.86776220743063</v>
+        <v>11.28597622274793</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556319671168148</v>
+        <v>0.7488613324145351</v>
       </c>
       <c r="G14" t="n">
-        <v>24.6517719897554</v>
+        <v>27.86058002474017</v>
       </c>
       <c r="H14" t="n">
-        <v>36.59254040272536</v>
+        <v>35.97886849216465</v>
       </c>
       <c r="I14" t="n">
-        <v>3.084094879414227</v>
+        <v>1.538176244212678</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722699794480092</v>
+        <v>4.680383327590843</v>
       </c>
       <c r="K14" t="n">
-        <v>16.84868537794446</v>
+        <v>16.18090058951578</v>
       </c>
       <c r="L14" t="n">
-        <v>44.34451025609717</v>
+        <v>42.17163147656619</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89732377990575</v>
+        <v>99.94875880300999</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.2444153627805</v>
+        <v>82.99462768845774</v>
       </c>
       <c r="C15" t="n">
-        <v>38.27342679719057</v>
+        <v>40.9840531365917</v>
       </c>
       <c r="D15" t="n">
-        <v>1.443067865936393</v>
+        <v>1.691006979580341</v>
       </c>
       <c r="E15" t="n">
-        <v>12.02537435394245</v>
+        <v>11.27360807607606</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564198864370498</v>
+        <v>0.7492548616277761</v>
       </c>
       <c r="G15" t="n">
-        <v>24.08847350063583</v>
+        <v>27.29172048059764</v>
       </c>
       <c r="H15" t="n">
-        <v>36.63069650359785</v>
+        <v>35.99777551165966</v>
       </c>
       <c r="I15" t="n">
-        <v>2.572758961999368</v>
+        <v>1.308418893742652</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72762429023156</v>
+        <v>4.682842885173599</v>
       </c>
       <c r="K15" t="n">
-        <v>17.7555846372195</v>
+        <v>17.00537231154225</v>
       </c>
       <c r="L15" t="n">
-        <v>43.88531926338398</v>
+        <v>41.96698349599151</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91433069779404</v>
+        <v>99.95640894412549</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.69100739375908</v>
+        <v>80.6773889471699</v>
       </c>
       <c r="C16" t="n">
-        <v>36.1172552715413</v>
+        <v>38.87007650294713</v>
       </c>
       <c r="D16" t="n">
-        <v>1.346164231194144</v>
+        <v>1.594387354144387</v>
       </c>
       <c r="E16" t="n">
-        <v>11.57550526994246</v>
+        <v>10.81127095025572</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570988396731494</v>
+        <v>0.7495925512654401</v>
       </c>
       <c r="G16" t="n">
-        <v>22.47090533720834</v>
+        <v>25.73234441522355</v>
       </c>
       <c r="H16" t="n">
-        <v>36.66357576864316</v>
+        <v>36.01399973173724</v>
       </c>
       <c r="I16" t="n">
-        <v>2.145890199140649</v>
+        <v>1.090840499134574</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731867747957183</v>
+        <v>4.684953445409</v>
       </c>
       <c r="K16" t="n">
-        <v>20.30899260624094</v>
+        <v>19.32261105283008</v>
       </c>
       <c r="L16" t="n">
-        <v>43.50228659549555</v>
+        <v>41.77096747495214</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92853447327778</v>
+        <v>99.96365503072936</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.33234229310409</v>
+        <v>84.75594197473876</v>
       </c>
       <c r="C17" t="n">
-        <v>37.30241971686382</v>
+        <v>41.60076536298306</v>
       </c>
       <c r="D17" t="n">
-        <v>1.347360540364033</v>
+        <v>1.595113504358191</v>
       </c>
       <c r="E17" t="n">
-        <v>12.34337347597771</v>
+        <v>12.26990118267216</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757771658236758</v>
+        <v>0.7499339468428404</v>
       </c>
       <c r="G17" t="n">
-        <v>22.88706395500195</v>
+        <v>27.0047634452791</v>
       </c>
       <c r="H17" t="n">
-        <v>37.0923471281728</v>
+        <v>37.29110145460702</v>
       </c>
       <c r="I17" t="n">
-        <v>2.168352671371113</v>
+        <v>1.158041273211712</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736072863979736</v>
+        <v>4.687087167767752</v>
       </c>
       <c r="K17" t="n">
-        <v>18.66765770689591</v>
+        <v>15.24405802526122</v>
       </c>
       <c r="L17" t="n">
-        <v>43.95770832921512</v>
+        <v>43.11659280864826</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92778575297486</v>
+        <v>99.96141619689256</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.91168624865092</v>
+        <v>86.14899287967978</v>
       </c>
       <c r="C18" t="n">
-        <v>35.21607367837325</v>
+        <v>42.24001881976376</v>
       </c>
       <c r="D18" t="n">
-        <v>1.259155619831495</v>
+        <v>1.596267562806597</v>
       </c>
       <c r="E18" t="n">
-        <v>11.83670501203933</v>
+        <v>12.79649620047844</v>
       </c>
       <c r="F18" t="n">
-        <v>0.758350494950633</v>
+        <v>0.7504765211516501</v>
       </c>
       <c r="G18" t="n">
-        <v>21.38876294580908</v>
+        <v>27.1273390255032</v>
       </c>
       <c r="H18" t="n">
-        <v>37.12068074567908</v>
+        <v>37.31808142221838</v>
       </c>
       <c r="I18" t="n">
-        <v>1.808340836899845</v>
+        <v>1.869853890323701</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739690593441455</v>
+        <v>4.690478257197812</v>
       </c>
       <c r="K18" t="n">
-        <v>21.0883137513491</v>
+        <v>13.85100712032021</v>
       </c>
       <c r="L18" t="n">
-        <v>43.63538055162846</v>
+        <v>43.84669065870501</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9397679813508</v>
+        <v>99.93771659878898</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.9703276449568</v>
+        <v>83.59896212276095</v>
       </c>
       <c r="C19" t="n">
-        <v>34.55190316283374</v>
+        <v>39.98025048223268</v>
       </c>
       <c r="D19" t="n">
-        <v>1.225536346402901</v>
+        <v>1.499161394402321</v>
       </c>
       <c r="E19" t="n">
-        <v>11.77212768167195</v>
+        <v>12.27790693349148</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588396440129708</v>
+        <v>0.7509430852405169</v>
       </c>
       <c r="G19" t="n">
-        <v>20.81768606027626</v>
+        <v>25.47709440915655</v>
       </c>
       <c r="H19" t="n">
-        <v>37.14462422076215</v>
+        <v>37.34128171718604</v>
       </c>
       <c r="I19" t="n">
-        <v>1.508765916749494</v>
+        <v>1.559180300530818</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742747775081066</v>
+        <v>4.693394282753229</v>
       </c>
       <c r="K19" t="n">
-        <v>22.0296723550432</v>
+        <v>16.40103787723904</v>
       </c>
       <c r="L19" t="n">
-        <v>43.36816470331655</v>
+        <v>43.56677125468595</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94974022119348</v>
+        <v>99.94805961415767</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.42075830945896</v>
+        <v>80.93973156869876</v>
       </c>
       <c r="C20" t="n">
-        <v>32.234171218637</v>
+        <v>37.56242808774683</v>
       </c>
       <c r="D20" t="n">
-        <v>1.133764838055679</v>
+        <v>1.398350588972929</v>
       </c>
       <c r="E20" t="n">
-        <v>11.10026594392286</v>
+        <v>11.66895031768692</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592615540710526</v>
+        <v>0.751345127359035</v>
       </c>
       <c r="G20" t="n">
-        <v>19.25880087856952</v>
+        <v>23.76389233699961</v>
       </c>
       <c r="H20" t="n">
-        <v>37.16527639765625</v>
+        <v>37.36127360246314</v>
       </c>
       <c r="I20" t="n">
-        <v>1.258003984239517</v>
+        <v>1.30001254922315</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745384712944077</v>
+        <v>4.695907045993968</v>
       </c>
       <c r="K20" t="n">
-        <v>24.57924169054104</v>
+        <v>19.06026843130125</v>
       </c>
       <c r="L20" t="n">
-        <v>43.1446769264678</v>
+        <v>43.33399291704828</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95808983564584</v>
+        <v>99.95668943609637</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.42300669359126</v>
+        <v>78.25442579561175</v>
       </c>
       <c r="C21" t="n">
-        <v>35.92921210612396</v>
+        <v>35.07778989643471</v>
       </c>
       <c r="D21" t="n">
-        <v>1.134617834092996</v>
+        <v>1.296997508963013</v>
       </c>
       <c r="E21" t="n">
-        <v>13.10170795202552</v>
+        <v>11.00382020444319</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598327898998337</v>
+        <v>0.7516920048073444</v>
       </c>
       <c r="G21" t="n">
-        <v>20.96008512830105</v>
+        <v>22.04147472558501</v>
       </c>
       <c r="H21" t="n">
-        <v>38.88003271156494</v>
+        <v>37.37852237773418</v>
       </c>
       <c r="I21" t="n">
-        <v>1.837775340832978</v>
+        <v>1.083843944033116</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748954936873959</v>
+        <v>4.698075030045901</v>
       </c>
       <c r="K21" t="n">
-        <v>18.57699330640872</v>
+        <v>21.74557420438826</v>
       </c>
       <c r="L21" t="n">
-        <v>45.43258146356857</v>
+        <v>43.14052443947639</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93878687610125</v>
+        <v>99.96388854029937</v>
       </c>
     </row>
   </sheetData>
